--- a/frontend/data/plantilla-agente-utopia.xlsx
+++ b/frontend/data/plantilla-agente-utopia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mriverius/Downloads/Repositories/travel-pioneers/frontend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC3FD2B-3FCE-7A47-98B7-7C5B175572A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0BB279-9586-114E-82CD-6F28C0CC5513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{705A2A06-CCAF-4902-AE72-D82AD645FD9B}"/>
   </bookViews>
@@ -34,416 +34,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={E5483EF5-DFD8-427F-8E79-D86EB6ACE262}</author>
-    <author>Beatriz</author>
-    <author>tc={D7F52F31-9D75-4631-BC12-7CD89561F15A}</author>
-    <author>tc={5DBA82C6-5792-499A-8041-C0FCE34427F7}</author>
-  </authors>
-  <commentList>
-    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{E5483EF5-DFD8-427F-8E79-D86EB6ACE262}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Fecha de firma de contrato, o de envío a TP</t>
-      </text>
-    </comment>
-    <comment ref="P6" authorId="1" shapeId="0" xr:uid="{02393792-FE96-4431-8936-0A6B6273DDF4}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Beatriz:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-S = Servicio
-N = Noches</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q6" authorId="1" shapeId="0" xr:uid="{6E663CB0-3DF9-4A10-A174-1BD9E92EDD1C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Beatriz:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Ver hoja</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R6" authorId="1" shapeId="0" xr:uid="{9A2AB219-C98B-4A92-AD19-442A1924E4E6}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Beatriz:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Ver Hoja</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S6" authorId="1" shapeId="0" xr:uid="{76CE72F4-4D4C-416B-8934-4F5BE0ABFE7D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Beatriz:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-SGL
-DBL
-TPL
-QDP
-QTN
-CHL
-DAY
-UNI
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="X6" authorId="1" shapeId="0" xr:uid="{4916627B-5EB8-4A5C-8ED2-C4C87EF965B5}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Beatriz:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-1 = FIJA
-2 = PORCENTUAL
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA6" authorId="1" shapeId="0" xr:uid="{021C5698-6C03-4829-9A97-1FB12508725F}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Beatriz:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-1 = FIJA
-2 = PORCENTUAL
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AB6" authorId="2" shapeId="0" xr:uid="{D7F52F31-9D75-4631-BC12-7CD89561F15A}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Que venga el # sin %
-</t>
-      </text>
-    </comment>
-    <comment ref="AC6" authorId="1" shapeId="0" xr:uid="{7BC0733F-34F3-46AF-88AA-1A66F10C134C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Beatriz:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-1 = VIE - DOM
-2 = JUE - DOM
-3 = VIE - LUN
-4 = VIE - SAB</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AD6" authorId="1" shapeId="0" xr:uid="{5841A776-2AC7-42DC-81B9-0AA9D7CE485B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Beatriz:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-1 = FIJA
-2 = PORCENTUAL
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AG6" authorId="1" shapeId="0" xr:uid="{DE8B8805-A0D3-47B7-8A3F-DA2288C53EF7}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Beatriz:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-1 = FIJA
-2 = PORCENTUAL
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AP6" authorId="1" shapeId="0" xr:uid="{EF5CA13F-42CD-4380-8FE2-DCEA2FE32392}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Beatriz:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-1 = contado
-2 = crédito
-3 = prepago</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AQ6" authorId="1" shapeId="0" xr:uid="{7203B069-F17B-49C3-B640-9C15EE56D447}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Beatriz:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-plazo de crédito en días o bien cantidad de días con que se debe prepagar</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AT6" authorId="1" shapeId="0" xr:uid="{A484192F-E135-465D-9CDF-60953740817A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Beatriz:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-LOC = Colones
-USD = Dólares</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AU6" authorId="3" shapeId="0" xr:uid="{5DBA82C6-5792-499A-8041-C0FCE34427F7}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    01: Banco de CR
-02: Banco Naciona 
-04: Banco Popular
-05: Citibank 
-06: Da vivienda
-07: Bac San Jose
-08: Scotia
-09: Lafise 
-10: Banco General
-11: Cuscatlan 
-12: Promerica
-13: BCT
-14: Paypal </t>
-      </text>
-    </comment>
-    <comment ref="AW6" authorId="1" shapeId="0" xr:uid="{2DD79158-507A-4CA5-A1D2-27BB3F51D2A8}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Beatriz:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-LOC = Colones
-USD = Dólares</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U7" authorId="1" shapeId="0" xr:uid="{B68F6293-13E7-44E6-BA01-78BE4486F816}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Beatriz:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-El formato de fecha debe ser YYYY-MM-DD</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="207">
   <si>
@@ -1076,7 +666,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1210,19 +800,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -1604,7 +1181,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1633,7 +1210,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="43"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="43"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1695,9 +1272,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Jennifer  Padilla" id="{C4F7596C-4E5C-4071-9BF5-8336879987E8}" userId="S::jennifer@travel-pioneers.com::fb822e4c-fef5-445a-bf3c-a06b73ab94a3" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2015,35 +1590,8 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="F6" dT="2026-04-28T15:53:30.04" personId="{C4F7596C-4E5C-4071-9BF5-8336879987E8}" id="{E5483EF5-DFD8-427F-8E79-D86EB6ACE262}">
-    <text>Fecha de firma de contrato, o de envío a TP</text>
-  </threadedComment>
-  <threadedComment ref="AB6" dT="2026-04-28T16:48:35.76" personId="{C4F7596C-4E5C-4071-9BF5-8336879987E8}" id="{D7F52F31-9D75-4631-BC12-7CD89561F15A}">
-    <text xml:space="preserve">Que venga el # sin %
-</text>
-  </threadedComment>
-  <threadedComment ref="AU6" dT="2026-04-28T17:43:25.91" personId="{C4F7596C-4E5C-4071-9BF5-8336879987E8}" id="{5DBA82C6-5792-499A-8041-C0FCE34427F7}">
-    <text xml:space="preserve">01: Banco de CR
-02: Banco Naciona 
-04: Banco Popular
-05: Citibank 
-06: Da vivienda
-07: Bac San Jose
-08: Scotia
-09: Lafise 
-10: Banco General
-11: Cuscatlan 
-12: Promerica
-13: BCT
-14: Paypal </text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C72AF7-A35A-4F3C-B64F-81CB8265B30E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C72AF7-A35A-4F3C-B64F-81CB8265B30E}">
   <dimension ref="A1:BA60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3291,10 +2839,9 @@
       <c r="AH60" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/frontend/data/plantilla-agente-utopia.xlsx
+++ b/frontend/data/plantilla-agente-utopia.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mriverius/Downloads/Repositories/travel-pioneers/frontend/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mriverius/Downloads/Repositories/travel-pioneers/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0BB279-9586-114E-82CD-6F28C0CC5513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D705BE91-5361-ED44-BD11-17F886EBDDED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{705A2A06-CCAF-4902-AE72-D82AD645FD9B}"/>
   </bookViews>
   <sheets>
-    <sheet name="MONTEVERDE_LODGE_CONTRACT_2026_" sheetId="1" r:id="rId1"/>
+    <sheet name="TARIFAS" sheetId="1" r:id="rId1"/>
     <sheet name="Tipos de Servicio" sheetId="2" r:id="rId2"/>
     <sheet name="Categorias" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -35,35 +35,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="207">
-  <si>
-    <t xml:space="preserve">Razon social </t>
-  </si>
-  <si>
-    <t>CÃ©dula JurÃ­dica</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="208">
   <si>
     <t xml:space="preserve">CONTRACT DATE </t>
   </si>
   <si>
-    <t xml:space="preserve">Nombre Comercial </t>
-  </si>
-  <si>
-    <t>País</t>
-  </si>
-  <si>
-    <t>TIPE OF BUSINESS</t>
-  </si>
-  <si>
     <t>CONTRACT STARTS</t>
   </si>
   <si>
     <t>CONTRACT ENDS</t>
   </si>
   <si>
-    <t xml:space="preserve">Product Name </t>
-  </si>
-  <si>
     <t xml:space="preserve">SEASON NAME </t>
   </si>
   <si>
@@ -76,15 +58,6 @@
     <t xml:space="preserve">MEALS INCLUDED </t>
   </si>
   <si>
-    <t xml:space="preserve">Precios NETO con IVA incluido </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precio RACK con IVA INCLUIDO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentaje de comision </t>
-  </si>
-  <si>
     <t>CANCELATION POLICY</t>
   </si>
   <si>
@@ -100,54 +73,9 @@
     <t>OTHER INCLUDED</t>
   </si>
   <si>
-    <t xml:space="preserve">Fees adicionales? </t>
-  </si>
-  <si>
     <t xml:space="preserve">RESERVATIONS EMAIL </t>
   </si>
   <si>
-    <t>Tipo Actividad</t>
-  </si>
-  <si>
-    <t>Proveedor</t>
-  </si>
-  <si>
-    <t>Cod.Servicio</t>
-  </si>
-  <si>
-    <t>Tipo Tarifa Neta</t>
-  </si>
-  <si>
-    <t>Tipo Tarifa Mayorista</t>
-  </si>
-  <si>
-    <t>T.Tar Neta Fin Semana</t>
-  </si>
-  <si>
-    <t>Precios NETO con IVA incluido Fin de Semana</t>
-  </si>
-  <si>
-    <t>Precio RACK con IVA INCLUIDO Fin de Semana</t>
-  </si>
-  <si>
-    <t>Tipo Tarifa Mayorista Fin de Semana</t>
-  </si>
-  <si>
-    <t>Porcentaje de comision  Fin de Semana</t>
-  </si>
-  <si>
-    <t>Tipo Tarifa Fin Semana</t>
-  </si>
-  <si>
-    <t>Zona Turismo</t>
-  </si>
-  <si>
-    <t>Tipo Unidad</t>
-  </si>
-  <si>
-    <t>Tipo Servicio</t>
-  </si>
-  <si>
     <t>Categoría</t>
   </si>
   <si>
@@ -613,15 +541,6 @@
     <t>Solo si hay tarifas de fin de semana</t>
   </si>
   <si>
-    <t>State/Province</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ocupación </t>
-  </si>
-  <si>
     <t>CUENTA BANCARIA 1</t>
   </si>
   <si>
@@ -656,6 +575,90 @@
   </si>
   <si>
     <t>NOTAS</t>
+  </si>
+  <si>
+    <t>TIPO ACTIVIDAD</t>
+  </si>
+  <si>
+    <t>ZONA TURISMO</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>RAZÓN SOCIAL</t>
+  </si>
+  <si>
+    <t>CÉDULA JURÍDICA</t>
+  </si>
+  <si>
+    <t>NOMBRE COMERCIAL</t>
+  </si>
+  <si>
+    <t>PAÍS</t>
+  </si>
+  <si>
+    <t>STATE/PROVINCE</t>
+  </si>
+  <si>
+    <t>LOCATION</t>
+  </si>
+  <si>
+    <t>TYPE OF BUSINESS</t>
+  </si>
+  <si>
+    <t>COD. SERVICIO</t>
+  </si>
+  <si>
+    <t>PRODUCT NAME</t>
+  </si>
+  <si>
+    <t>TIPO UNIDAD</t>
+  </si>
+  <si>
+    <t>TIPO SERVICIO</t>
+  </si>
+  <si>
+    <t>CATEGORÍA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCUPACIÓN </t>
+  </si>
+  <si>
+    <t>TIPO TARIFA NETA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRECIOS NETO CON IVA INCLUIDO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRECIO RACK CON IVA INCLUIDO </t>
+  </si>
+  <si>
+    <t>TIPO TARIFA MAYORISTA</t>
+  </si>
+  <si>
+    <t>PORCENTAJE DE COMISIÓN</t>
+  </si>
+  <si>
+    <t>TIPO TARIFA FIN DE SEMANA</t>
+  </si>
+  <si>
+    <t>TIPO TARIFA NETO FIN DE SEMANA</t>
+  </si>
+  <si>
+    <t>PRECIOS NETO CON IVA INCLUIDO FIN DE SEMANA</t>
+  </si>
+  <si>
+    <t>PRECIO RACK CON IVA INCLUIDO FIN DE SEMANA</t>
+  </si>
+  <si>
+    <t>TIPO TARIFA MAYORISTA FIN DE SEMANA</t>
+  </si>
+  <si>
+    <t>PORCENTAJE DE COMISIÓN FIN DE SEMANA</t>
+  </si>
+  <si>
+    <t>FEES ADICIONALES?</t>
   </si>
 </sst>
 </file>
@@ -1271,10 +1274,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1597,14 +1596,18 @@
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.1640625" customWidth="1"/>
+    <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.33203125" customWidth="1"/>
     <col min="9" max="9" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.5" customWidth="1"/>
     <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="22.83203125" bestFit="1" customWidth="1"/>
     <col min="16" max="18" width="13.5" customWidth="1"/>
     <col min="20" max="20" width="17.83203125" bestFit="1" customWidth="1"/>
@@ -1617,11 +1620,11 @@
     <col min="27" max="27" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="22.83203125" style="13" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="22.83203125" customWidth="1"/>
-    <col min="30" max="30" width="15" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="35" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="53" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="40.5" customWidth="1"/>
     <col min="37" max="37" width="36.6640625" bestFit="1" customWidth="1"/>
@@ -1638,186 +1641,186 @@
     <row r="1" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
       <c r="B1" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A2" s="11"/>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A3" s="12"/>
       <c r="B3" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:53" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>23</v>
+        <v>180</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>34</v>
+        <v>181</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="G6" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="M6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="N6" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="P6" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q6" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="R6" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="T6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="U6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="K6" s="5" t="s">
+      <c r="V6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="W6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="X6" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA6" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="AB6" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="AC6" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="AD6" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="AE6" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="AF6" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="AG6" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AH6" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="AI6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" s="5" t="s">
+      <c r="AJ6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="P6" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q6" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="R6" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="T6" s="5" t="s">
+      <c r="AK6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="U6" s="5" t="s">
+      <c r="AL6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="V6" s="5" t="s">
+      <c r="AM6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="W6" s="5" t="s">
+      <c r="AN6" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AO6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="X6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB6" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="AK6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AL6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AN6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AO6" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="AP6" s="5" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="AQ6" s="5" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="AR6" s="5" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="AS6" s="5" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="AT6" s="5" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="AU6" s="5" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="AV6" s="5" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="AW6" s="5" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="AX6" s="5" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="AY6" s="5" t="s">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="AZ6" s="5" t="s">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="BA6" s="5" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:53" x14ac:dyDescent="0.2">
@@ -2855,202 +2858,202 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -3070,783 +3073,783 @@
   <sheetData>
     <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C40" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C41" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C43" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C44" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="C46" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B47" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="C47" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C49" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="C50" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="C51" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="C52" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C53" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="C54" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C55" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C56" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="B57" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C57" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C58" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B59" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="C59" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B60" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="C60" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B61" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="C61" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B62" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="C62" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="C63" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B64" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="C64" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B65" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="C65" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B66" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="C66" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B67" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="C67" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="C68" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C71" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
